--- a/order_generation/PO_excel_export/test1-2.xlsx
+++ b/order_generation/PO_excel_export/test1-2.xlsx
@@ -350,7 +350,7 @@
       <row>6</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1104900" cy="1266825"/>
+    <ext cx="1562100" cy="1266825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -358,6 +358,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1362075" cy="1266825"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -761,7 +786,7 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>XX印刷厂</t>
+          <t>义乌市一柠饰品有限公司</t>
         </is>
       </c>
       <c r="C3" s="16" t="n"/>
@@ -785,7 +810,11 @@
           <t>电话：</t>
         </is>
       </c>
-      <c r="B4" s="16" t="inlineStr"/>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>0574-27889688</t>
+        </is>
+      </c>
       <c r="C4" s="16" t="n"/>
       <c r="D4" s="16" t="n"/>
       <c r="E4" s="16" t="n"/>
@@ -796,7 +825,7 @@
       </c>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>2025年11月04日</t>
+          <t>2025年12月30日</t>
         </is>
       </c>
       <c r="H4" s="16" t="n"/>
@@ -807,11 +836,7 @@
           <t>联系人：</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>XX印刷厂</t>
-        </is>
-      </c>
+      <c r="B5" s="16" t="inlineStr"/>
       <c r="C5" s="16" t="n"/>
       <c r="D5" s="16" t="n"/>
       <c r="E5" s="16" t="n"/>
@@ -822,7 +847,7 @@
       </c>
       <c r="G5" s="18" t="inlineStr">
         <is>
-          <t>孙诚昱</t>
+          <t>郑遥杰</t>
         </is>
       </c>
       <c r="H5" s="16" t="n"/>
@@ -868,17 +893,17 @@
     <row r="7" ht="100" customFormat="1" customHeight="1" s="2">
       <c r="A7" s="29" t="inlineStr">
         <is>
-          <t>EC221-1-1</t>
+          <t>EEHB-NBB-1C</t>
         </is>
       </c>
       <c r="B7" s="29" t="n"/>
       <c r="C7" s="29" t="inlineStr">
         <is>
-          <t>鱼骨梳包装，350g白卡双面印刷，FSC 绿色</t>
+          <t>浅咖色</t>
         </is>
       </c>
       <c r="D7" s="29" t="n">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="E7" s="29" t="n">
         <v>0.45</v>
@@ -890,14 +915,29 @@
       <c r="G7" s="29" t="inlineStr"/>
       <c r="H7" s="20" t="n"/>
     </row>
-    <row r="8" ht="100.15" customFormat="1" customHeight="1" s="2">
-      <c r="A8" s="29" t="n"/>
+    <row r="8" ht="100" customFormat="1" customHeight="1" s="2">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>EEHB-NBB-1B</t>
+        </is>
+      </c>
       <c r="B8" s="29" t="n"/>
-      <c r="C8" s="29" t="n"/>
-      <c r="D8" s="29" t="n"/>
-      <c r="E8" s="29" t="n"/>
-      <c r="F8" s="29" t="n"/>
-      <c r="G8" s="29" t="n"/>
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F8" s="29">
+        <f>D8*E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="29" t="inlineStr"/>
       <c r="H8" s="20" t="n"/>
     </row>
     <row r="9" ht="100.15" customFormat="1" customHeight="1" s="2">
@@ -948,7 +988,7 @@
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>瑾秀 收货信息是瑾秀：浙江宁波市余姚市陆埠镇五马工业区创利西路 15 号 18067420259 多多</t>
+          <t>瑾秀地址：浙江宁波市余姚市陆埠镇五马工业区创利西路 15 号 多多 15258337865</t>
         </is>
       </c>
       <c r="C12" s="25" t="n"/>
@@ -966,7 +1006,7 @@
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>出货后45天凭增值税发票付款</t>
+          <t>开专票，价格已含税运</t>
         </is>
       </c>
       <c r="C13" s="25" t="n"/>
@@ -992,7 +1032,7 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>2025年11月11日</t>
+          <t>2026年01月14日</t>
         </is>
       </c>
       <c r="C14" s="25" t="n"/>
@@ -1061,7 +1101,10 @@
     <row r="19" ht="17.25" customFormat="1" customHeight="1" s="4">
       <c r="A19" s="25" t="inlineStr">
         <is>
-          <t>放2%余量</t>
+          <t>义乌市一柠饰品有限公司
+税号:91330782MA2HQR5A51
+对公账号:201000320634668
+开户行:浙江义乌农村商业银行股份有限公司鹏城支行</t>
         </is>
       </c>
       <c r="B19" s="25" t="n"/>
@@ -1073,7 +1116,11 @@
       <c r="H19" s="25" t="n"/>
     </row>
     <row r="20" ht="17.25" customFormat="1" customHeight="1" s="4">
-      <c r="A20" s="25" t="inlineStr"/>
+      <c r="A20" s="25" t="inlineStr">
+        <is>
+          <t>开专票，价格已含税运</t>
+        </is>
+      </c>
       <c r="B20" s="25" t="n"/>
       <c r="C20" s="25" t="n"/>
       <c r="D20" s="25" t="n"/>
@@ -1083,7 +1130,11 @@
       <c r="H20" s="25" t="n"/>
     </row>
     <row r="21" ht="17.25" customFormat="1" customHeight="1" s="4">
-      <c r="A21" s="25" t="inlineStr"/>
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>瑾秀地址：浙江宁波市余姚市陆埠镇五马工业区创利西路 15 号 多多 15258337865</t>
+        </is>
+      </c>
       <c r="B21" s="25" t="n"/>
       <c r="C21" s="25" t="n"/>
       <c r="D21" s="25" t="n"/>
@@ -1338,7 +1389,7 @@
       <c r="D69" s="8" t="n"/>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>XX印刷厂</t>
+          <t>义乌市一柠饰品有限公司</t>
         </is>
       </c>
       <c r="F69" s="9" t="n"/>
